--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260817.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>134,785</t>
+          <t>134,285</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.55%</t>
+          <t>27.48%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.46%</t>
+          <t>8.62%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>97,630</t>
+          <t>97,430</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.63%</t>
+          <t>7.45%</t>
         </is>
       </c>
     </row>
@@ -682,310 +682,310 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>6.06%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>338,018,228</t>
+          <t>118,395</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.32%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>118,395</t>
+          <t>58,240</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>58,240</t>
+          <t>5,585</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,585</t>
+          <t>64,005</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>64,005</t>
+          <t>17,853</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>17,953</t>
+          <t>44,115</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>44,115</t>
+          <t>19,285</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,285</t>
+          <t>75,045</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>75,295</t>
+          <t>19,845</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>19,845</t>
+          <t>30,770</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>30,870</t>
+          <t>119,481,380</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>49,945</t>
+          <t>3,560,612</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>11,451</t>
+          <t>49,945</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>3,085,437</t>
+          <t>11,451</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,39 +997,39 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>35,430</t>
+          <t>25,928</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>18,990</t>
+          <t>35,430</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>25,928</t>
+          <t>18,990</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>58,108</t>
+          <t>58,008</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,44 +1085,44 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,790</t>
+          <t>9,336</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,336</t>
+          <t>7,790</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>19,237</t>
+          <t>19,137</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>141,210,000</t>
+          <t>96,005,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,370,817</t>
+          <t>298,882</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
